--- a/Result/profitability/2313.xlsx
+++ b/Result/profitability/2313.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2025</v>
+        <v>1.16875</v>
       </c>
       <c r="N2" t="n">
-        <v>17.11125</v>
+        <v>17.18125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.11</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.98125</v>
       </c>
       <c r="N3" t="n">
-        <v>15.37875</v>
+        <v>15.6525</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.25</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8574999999999999</v>
+        <v>0.875</v>
       </c>
       <c r="N4" t="n">
-        <v>14.72</v>
+        <v>14.8875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.03</v>
       </c>
       <c r="M5" t="n">
-        <v>0.72375</v>
+        <v>0.79125</v>
       </c>
       <c r="N5" t="n">
-        <v>13.84</v>
+        <v>13.87375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6375</v>
+        <v>0.5662499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>12.7725</v>
+        <v>12.5925</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.18</v>
       </c>
       <c r="M7" t="n">
-        <v>0.38875</v>
+        <v>0.30625</v>
       </c>
       <c r="N7" t="n">
-        <v>10.66625</v>
+        <v>10.6425</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.16</v>
       </c>
       <c r="M8" t="n">
-        <v>0.13125</v>
+        <v>0.12875</v>
       </c>
       <c r="N8" t="n">
-        <v>8.762499999999999</v>
+        <v>8.828749999999999</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>-0.06875000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>6.39875</v>
+        <v>6.398750000000001</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>-0.12125</v>
       </c>
       <c r="N11" t="n">
-        <v>5.3225</v>
+        <v>5.322500000000001</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>19992</v>
+      </c>
+      <c r="D75" t="n">
+        <v>16291</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3701</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1952</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.76%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-156</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1795</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1479</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.36375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.1025</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.01587301587301593</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.5300000000000011</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.02947719688542838</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.7714285714285716</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.2700000000000031</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.01480263157894757</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
